--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2019_los_rios.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2019_los_rios.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 09:06</t>
+    <t xml:space="preserve">2026-09-08 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
